--- a/output/pdf_financials_xlsx/ADZ.xlsx
+++ b/output/pdf_financials_xlsx/ADZ.xlsx
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.017161</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001349</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-12.402434</v>
+        <v>-12.419595</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.318243</v>
+        <v>-2.319592</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.108646</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-12.397834</v>
+        <v>-12.414995</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.30381</v>
+        <v>-2.305159</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.091141</v>
@@ -1998,43 +1998,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.353135</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.07449600000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.050825</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.008609</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.43977</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.980924</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.138748</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.158383</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.764987</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.699021</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.260448</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.602811</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.323202</v>
       </c>
     </row>
     <row r="35">
@@ -2090,43 +2090,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.353135</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.002277</v>
+        <v>0.07677299999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.000477</v>
+        <v>0.051302</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.008609</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.43977</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.980924</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.138748</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.158383</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.185</v>
+        <v>1.949987</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.095</v>
+        <v>0.794021</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.075</v>
+        <v>0.335448</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.602811</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.323202</v>
       </c>
     </row>
     <row r="37">
@@ -2642,43 +2642,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.378947</v>
+        <v>0.025812</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.105711</v>
+        <v>0.031215</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.060579</v>
+        <v>0.009754000000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.011677</v>
+        <v>0.003068</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.444032</v>
+        <v>0.004262</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.038827</v>
+        <v>0.057903</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.173486</v>
+        <v>0.034738</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.537075</v>
+        <v>0.378692</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.214473</v>
+        <v>0.449486</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.056196</v>
+        <v>0.357175</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.6672979999999999</v>
+        <v>0.40685</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.886366</v>
+        <v>0.283555</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.330486</v>
+        <v>0.007284</v>
       </c>
     </row>
     <row r="49">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E320" s="5" t="n">

--- a/output/pdf_financials_xlsx/ADZ.xlsx
+++ b/output/pdf_financials_xlsx/ADZ.xlsx
@@ -1730,22 +1730,22 @@
         <v>0.00186</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.001503</v>
+        <v>0.012545</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.0008229999999999999</v>
+        <v>0.014154</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.000614</v>
+        <v>0.014155</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.00046</v>
+        <v>0.014155</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.000346</v>
+        <v>0.014154</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.00026</v>
+        <v>0.009436999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1776,22 +1776,22 @@
         <v>-0.680444</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.550336</v>
+        <v>-0.5392940000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.48338</v>
+        <v>-0.470049</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.040954</v>
+        <v>-1.027413</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.345252</v>
+        <v>-1.331557</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.125273</v>
+        <v>-3.111465</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.539733</v>
+        <v>-5.530556</v>
       </c>
     </row>
     <row r="30">
@@ -5136,22 +5136,22 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.012545</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.014154</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.014155</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.014155</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.014154</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.009436999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -13069,7 +13069,11 @@
           <t>Depreciation of right-of-use asset 8</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -18566,7 +18570,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -23214,7 +23222,11 @@
           <t>Depreciation of right-of-use asset 8</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -25520,7 +25532,11 @@
           <t>Depreciation of right-of-use asset 8 3,539 3,539</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -28141,7 +28157,11 @@
           <t>Depreciation of right-of-use assets 7</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
